--- a/frontend/public/originals/qc-ruler-verification.xlsx
+++ b/frontend/public/originals/qc-ruler-verification.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parth\Desktop\dcrs-orig-wt\frontend\public\originals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parth\Desktop\dcrs-calib-wt\frontend\public\originals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03CC2F39-A3FE-457C-BA60-0A3FF7BEC807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1363BDD8-C920-4ED0-82B3-E5E50795264F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="4" sheetId="10" r:id="rId1"/>
+    <sheet name="36" sheetId="50" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -81,6 +81,9 @@
     <t>200 mm</t>
   </si>
   <si>
+    <t>500 mm</t>
+  </si>
+  <si>
     <t>1 mm</t>
   </si>
   <si>
@@ -111,18 +114,6 @@
     <t>0 - 600 mm</t>
   </si>
   <si>
-    <t>290 mm</t>
-  </si>
-  <si>
-    <t>50 mm</t>
-  </si>
-  <si>
-    <t>150 mm</t>
-  </si>
-  <si>
-    <t>250 mm</t>
-  </si>
-  <si>
     <t>Kapila Barad</t>
   </si>
   <si>
@@ -132,7 +123,16 @@
     <t>Ajanta</t>
   </si>
   <si>
-    <t>GP-3/MS/04</t>
+    <t>490 mm</t>
+  </si>
+  <si>
+    <t>0-600mm</t>
+  </si>
+  <si>
+    <t>300 mm</t>
+  </si>
+  <si>
+    <t>400 mm</t>
   </si>
   <si>
     <t>CAL/LPI/GP-23/23</t>
@@ -150,7 +150,7 @@
     <t>23.09.2025</t>
   </si>
   <si>
-    <t>0-600 mm</t>
+    <t>GP-3/MS/36</t>
   </si>
 </sst>
 </file>
@@ -1180,7 +1180,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1195,14 +1195,14 @@
   <sheetData>
     <row r="1" spans="1:6" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
       <c r="D1" s="24"/>
       <c r="E1" s="25"/>
       <c r="F1" s="29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="8.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1215,7 +1215,7 @@
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="32"/>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="5" spans="1:6" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="21"/>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B7" s="41"/>
       <c r="C7" s="41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="41"/>
       <c r="E7" s="41"/>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B8" s="41"/>
       <c r="C8" s="41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="41"/>
       <c r="E8" s="41"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B9" s="41"/>
       <c r="C9" s="41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D9" s="41"/>
       <c r="E9" s="41"/>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="14" spans="1:6" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="46" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="47"/>
       <c r="C14" s="47"/>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="49" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D15" s="50"/>
       <c r="E15" s="50"/>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B16" s="41"/>
       <c r="C16" s="52" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B17" s="41"/>
       <c r="C17" s="52" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D17" s="52"/>
       <c r="E17" s="52"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B18" s="41"/>
       <c r="C18" s="52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D18" s="52"/>
       <c r="E18" s="52"/>
@@ -1438,7 +1438,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>11</v>
@@ -1455,19 +1455,19 @@
         <v>1</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C24" s="18">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D24" s="12">
         <v>0</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F24" s="61" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1475,11 +1475,11 @@
         <f t="shared" ref="A25:A29" si="0">A24+1</f>
         <v>2</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>14</v>
+      <c r="B25" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="C25" s="18">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D25" s="12">
         <v>0</v>
@@ -1493,10 +1493,10 @@
         <v>3</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" s="18">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="D26" s="12">
         <v>0</v>
@@ -1510,10 +1510,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C27" s="18">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D27" s="12">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C28" s="18">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="D28" s="12">
         <v>0</v>
@@ -1544,10 +1544,10 @@
         <v>6</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C29" s="16">
-        <v>290</v>
+        <v>590</v>
       </c>
       <c r="D29" s="17">
         <v>0</v>
@@ -1557,6 +1557,36 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="E24:E29"/>
+    <mergeCell ref="F24:F29"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:F9"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="A1:E2"/>
@@ -1564,36 +1594,6 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="E24:E29"/>
-    <mergeCell ref="F24:F29"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.75" bottom="0" header="0" footer="0"/>
